--- a/artfynd/A 3700-2024 artfynd.xlsx
+++ b/artfynd/A 3700-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3700-2024 artfynd.xlsx
+++ b/artfynd/A 3700-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81217573</v>
+        <v>81217591</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424072.1188564962</v>
+        <v>423999</v>
       </c>
       <c r="R2" t="n">
-        <v>6459497.984626325</v>
+        <v>6459508</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,10 +770,328 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson, Frida Nettelbladt</t>
+          <t>Frida Nettelbladt, Erik Edvardsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>81217573</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Falköpings kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>424072</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459498</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observatör: Frida Nettelbladt. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt, Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81217583</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Falköpings kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424036</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459465</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observatör: Frida Nettelbladt. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt, Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>81217585</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Falköpings kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>424047</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6459461</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stenstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Observatör: Frida Nettelbladt. Naturvärdesinventering för Falköpings kommun. Calluna AB (JSN0108).</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt, Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturvärdesinventering av kommunal mark i Falköpings kommun 2018-2019</t>
         </is>
